--- a/outputs/Block5_Least_Stable.xlsx
+++ b/outputs/Block5_Least_Stable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="54">
   <si>
     <t>Variable</t>
   </si>
@@ -106,49 +106,52 @@
     <t>Model Stability</t>
   </si>
   <si>
+    <t>RPP</t>
+  </si>
+  <si>
+    <t>DPP</t>
+  </si>
+  <si>
+    <t>RSenTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DSenSafResLR (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
+    <t>DHouLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
     <t>RSenLikResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>DHouSafResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>RPP</t>
+    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>RSenLeanResLD  (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DPP</t>
-  </si>
-  <si>
-    <t>RSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
-    <t>DHouTiltResH (&lt;=1%)</t>
-  </si>
-  <si>
-    <t>DSenSafResLR (&gt;10%)</t>
-  </si>
-  <si>
     <t>RHouTiltResLD (&lt;=1%)</t>
   </si>
   <si>
-    <t>RSenLikResLD (&gt;5%&lt;=10%)</t>
+    <t>RHouLeanResLD  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>DSenLikResLR (&gt;5%&lt;=10%)</t>
   </si>
   <si>
     <t>DSenTiltResH (&lt;=1%)</t>
   </si>
   <si>
-    <t>DHouLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
+    <t>Popular Vote</t>
   </si>
   <si>
     <t>Senate Buckets</t>
@@ -157,22 +160,22 @@
     <t>House Buckets</t>
   </si>
   <si>
-    <t>Popular Vote</t>
-  </si>
-  <si>
     <t>ML Predicted</t>
   </si>
   <si>
+    <t>Continuous</t>
+  </si>
+  <si>
     <t>Integer</t>
   </si>
   <si>
-    <t>Continuous</t>
-  </si>
-  <si>
     <t>Very high sensitivity</t>
   </si>
   <si>
     <t>High sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate sensitivity</t>
   </si>
 </sst>
 </file>
@@ -633,79 +636,85 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>1.148</v>
+        <v>0.4686639999999987</v>
       </c>
       <c r="D2">
-        <v>1.224</v>
+        <v>0.4831359999999993</v>
       </c>
       <c r="E2">
-        <v>2.2065080011038</v>
+        <v>0.4848653204771308</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0.484</v>
       </c>
       <c r="G2">
-        <v>1.183721905632348</v>
+        <v>0.4749155896970425</v>
+      </c>
+      <c r="H2">
+        <v>0.4501181038374718</v>
+      </c>
+      <c r="I2">
+        <v>0.4501181038374718</v>
       </c>
       <c r="J2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>2.2065080011038</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="L2">
-        <v>0.8500971208676269</v>
+        <v>0.01064148394560983</v>
       </c>
       <c r="M2">
-        <v>1.038416113387647</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="N2">
-        <v>0.5</v>
+        <v>0.0385</v>
       </c>
       <c r="O2" t="s">
         <v>48</v>
       </c>
       <c r="P2">
-        <v>2.558978028396561</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="Q2">
-        <v>1.159741105455516</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>0.4501181038374718</v>
       </c>
       <c r="S2" t="s">
         <v>49</v>
       </c>
       <c r="T2">
-        <v>0.3524700272927612</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.4410219716034391</v>
+        <v>0</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
       </c>
       <c r="W2">
-        <v>1.183721905632348</v>
+        <v>0.4749155896970425</v>
       </c>
       <c r="X2">
-        <v>1.022786095471451</v>
+        <v>0.02479748585957076</v>
       </c>
       <c r="Y2">
-        <v>0.7934919988962004</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>1.203140288756154</v>
+        <v>2.330265777434267</v>
       </c>
       <c r="AA2">
-        <v>0.933413347037743</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1.700194241735254</v>
+        <v>0.2764021804054501</v>
       </c>
       <c r="AC2">
-        <v>32.99758334560023</v>
+        <v>21.98801276749871</v>
       </c>
       <c r="AD2" t="s">
         <v>51</v>
@@ -716,85 +725,91 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3">
-        <v>173.312</v>
+        <v>0.5025559999999998</v>
       </c>
       <c r="D3">
-        <v>170.552</v>
+        <v>0.4879279999999993</v>
       </c>
       <c r="E3">
-        <v>176.0063243272117</v>
+        <v>0.4850537176443364</v>
       </c>
       <c r="F3">
-        <v>169.2</v>
+        <v>0.4868</v>
       </c>
       <c r="G3">
-        <v>171.9799070682415</v>
+        <v>0.4962370216909646</v>
+      </c>
+      <c r="H3">
+        <v>0.5206818961625282</v>
+      </c>
+      <c r="I3">
+        <v>0.5206818961625282</v>
       </c>
       <c r="J3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K3">
-        <v>176.0063243272117</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="L3">
-        <v>4.764861070548267</v>
+        <v>0.01323492690170848</v>
       </c>
       <c r="M3">
-        <v>5.24749619700716</v>
+        <v>0.01193820542365915</v>
       </c>
       <c r="N3">
-        <v>13.2</v>
+        <v>0.04170000000000001</v>
       </c>
       <c r="O3" t="s">
         <v>48</v>
       </c>
       <c r="P3">
-        <v>181.3185762509099</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="Q3">
-        <v>1.030182165010288</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>181</v>
+        <v>0.5206818961625282</v>
       </c>
       <c r="S3" t="s">
         <v>49</v>
       </c>
       <c r="T3">
-        <v>5.31225192369817</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>-0.3185762509098993</v>
+        <v>0</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>171.9799070682415</v>
+        <v>0.4962370216909646</v>
       </c>
       <c r="X3">
-        <v>4.026417258970184</v>
+        <v>0.02444487447156363</v>
       </c>
       <c r="Y3">
-        <v>4.993675672788271</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>0.845023013127828</v>
+        <v>1.8469973165026</v>
       </c>
       <c r="AA3">
-        <v>1.04802125368446</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.3609743235263839</v>
+        <v>0.317384338170467</v>
       </c>
       <c r="AC3">
-        <v>40.00873433552916</v>
+        <v>30.10291257195357</v>
       </c>
       <c r="AD3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:30">
@@ -802,28 +817,28 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C4">
-        <v>0.192</v>
+        <v>0.164</v>
       </c>
       <c r="D4">
-        <v>0.3</v>
+        <v>0.268</v>
       </c>
       <c r="E4">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="F4">
         <v>0.2</v>
       </c>
       <c r="G4">
-        <v>0.2427627080038635</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>0.851191504820574</v>
+        <v>0.6905082799680116</v>
       </c>
       <c r="L4">
         <v>0.4925498319332764</v>
@@ -838,46 +853,46 @@
         <v>48</v>
       </c>
       <c r="P4">
-        <v>0.9871617767549565</v>
+        <v>0.7880676051329962</v>
       </c>
       <c r="Q4">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R4">
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T4">
-        <v>0.1359702719343825</v>
+        <v>0.09755932516498467</v>
       </c>
       <c r="U4">
-        <v>0.01283822324504347</v>
+        <v>0.2119323948670038</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>0.2427627080038635</v>
+        <v>0.2128826077074241</v>
       </c>
       <c r="X4">
-        <v>0.6084287968167106</v>
+        <v>0.4776256722605874</v>
       </c>
       <c r="Y4">
-        <v>0.148808495179426</v>
+        <v>0.3094917200319884</v>
       </c>
       <c r="Z4">
-        <v>1.23526343401358</v>
+        <v>0.9697002035020272</v>
       </c>
       <c r="AA4">
-        <v>0.3021186599442072</v>
+        <v>0.6283460067730039</v>
       </c>
       <c r="AB4">
         <v>1.231374579833191</v>
       </c>
       <c r="AC4">
-        <v>40.30628543413643</v>
+        <v>42.73182468197061</v>
       </c>
       <c r="AD4" t="s">
         <v>52</v>
@@ -888,88 +903,82 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5">
-        <v>0.4696599999999989</v>
+        <v>10.028</v>
       </c>
       <c r="D5">
-        <v>0.4840119999999993</v>
+        <v>11.468</v>
       </c>
       <c r="E5">
-        <v>0.485114447962659</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="F5">
-        <v>0.484</v>
+        <v>11.6</v>
       </c>
       <c r="G5">
-        <v>0.4758597523032031</v>
-      </c>
-      <c r="H5">
-        <v>0.4614786298342541</v>
-      </c>
-      <c r="I5">
-        <v>0.4614786298342541</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="J5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>0.4614786298342541</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="L5">
-        <v>0.01064148394560983</v>
+        <v>3.050242274051084</v>
       </c>
       <c r="M5">
-        <v>0.01193820542365915</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N5">
-        <v>0.0385</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="s">
         <v>48</v>
       </c>
       <c r="P5">
-        <v>0.4614786298342541</v>
+        <v>15.15860750983988</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R5">
-        <v>0.4614786298342541</v>
+        <v>15</v>
       </c>
       <c r="S5" t="s">
         <v>50</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.876569357081072</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>-0.158607509839884</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>0.4758597523032031</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="X5">
-        <v>0.01438112246894896</v>
+        <v>2.577202046040632</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.717961847241188</v>
       </c>
       <c r="Z5">
-        <v>1.351420773874486</v>
+        <v>0.8449171621432557</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.5632214404266095</v>
       </c>
       <c r="AB5">
-        <v>0.2764021804054501</v>
+        <v>0.544686120366265</v>
       </c>
       <c r="AC5">
-        <v>41.5437331399677</v>
+        <v>47.41063290551929</v>
       </c>
       <c r="AD5" t="s">
         <v>52</v>
@@ -980,82 +989,82 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6">
-        <v>0.736</v>
+        <v>1.736</v>
       </c>
       <c r="D6">
-        <v>0.672</v>
+        <v>1.98</v>
       </c>
       <c r="E6">
-        <v>1.081403752400103</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="F6">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
-        <v>0.7059183952569696</v>
+        <v>1.850686118082802</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>1.081403752400103</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="L6">
-        <v>0.3332002265469857</v>
+        <v>1.736334852416627</v>
       </c>
       <c r="M6">
         <v>1.038416113387647</v>
       </c>
       <c r="N6">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="s">
         <v>48</v>
       </c>
       <c r="P6">
-        <v>1.254148383252238</v>
+        <v>0.05816049090560802</v>
       </c>
       <c r="Q6">
-        <v>1.159741105455516</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T6">
-        <v>0.1727446308521352</v>
+        <v>-0.009391135269987715</v>
       </c>
       <c r="U6">
-        <v>-0.254148383252238</v>
+        <v>-0.05816049090560802</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>0.7059183952569696</v>
+        <v>1.850686118082802</v>
       </c>
       <c r="X6">
-        <v>0.3754853571431331</v>
+        <v>1.783134491907207</v>
       </c>
       <c r="Y6">
-        <v>0.08140375240010278</v>
+        <v>0.06755162617559574</v>
       </c>
       <c r="Z6">
-        <v>1.126906067965067</v>
+        <v>1.026953118763609</v>
       </c>
       <c r="AA6">
-        <v>0.2443088146839053</v>
+        <v>0.03890472283130038</v>
       </c>
       <c r="AB6">
-        <v>0.5553337109116429</v>
+        <v>0.5601080169085895</v>
       </c>
       <c r="AC6">
-        <v>44.13147102701663</v>
+        <v>50.60417110498163</v>
       </c>
       <c r="AD6" t="s">
         <v>52</v>
@@ -1066,28 +1075,28 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7">
-        <v>13.152</v>
+        <v>13.232</v>
       </c>
       <c r="D7">
-        <v>12.22</v>
+        <v>12.328</v>
       </c>
       <c r="E7">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="F7">
         <v>12.4</v>
       </c>
       <c r="G7">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="L7">
         <v>2.351026032651849</v>
@@ -1102,46 +1111,46 @@
         <v>48</v>
       </c>
       <c r="P7">
-        <v>9.132471991736034</v>
+        <v>9.674452691001546</v>
       </c>
       <c r="Q7">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T7">
-        <v>-2.04240542473641</v>
+        <v>-1.562127356038731</v>
       </c>
       <c r="U7">
-        <v>-0.1324719917360344</v>
+        <v>0.3255473089984537</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="X7">
-        <v>1.539059214457176</v>
+        <v>1.570517285964419</v>
       </c>
       <c r="Y7">
-        <v>2.174877416472444</v>
+        <v>1.236580047040277</v>
       </c>
       <c r="Z7">
-        <v>0.6546329955866917</v>
+        <v>0.6680135669076143</v>
       </c>
       <c r="AA7">
-        <v>0.9250758546553748</v>
+        <v>0.5259746297430284</v>
       </c>
       <c r="AB7">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC7">
-        <v>47.27029992542463</v>
+        <v>53.88597538332969</v>
       </c>
       <c r="AD7" t="s">
         <v>52</v>
@@ -1155,85 +1164,79 @@
         <v>47</v>
       </c>
       <c r="C8">
-        <v>0.5015439999999998</v>
+        <v>13.58</v>
       </c>
       <c r="D8">
-        <v>0.4872199999999994</v>
+        <v>14.788</v>
       </c>
       <c r="E8">
-        <v>0.487434430017597</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="F8">
-        <v>0.4868</v>
+        <v>14.6</v>
       </c>
       <c r="G8">
-        <v>0.4953563430886915</v>
-      </c>
-      <c r="H8">
-        <v>0.5093213701657459</v>
-      </c>
-      <c r="I8">
-        <v>0.5093213701657459</v>
+        <v>14.16303197882762</v>
       </c>
       <c r="J8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8">
-        <v>0.5093213701657459</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="L8">
-        <v>0.01323492690170848</v>
+        <v>5.333756871724871</v>
       </c>
       <c r="M8">
-        <v>0.01193820542365915</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>0.04170000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="O8" t="s">
         <v>48</v>
       </c>
       <c r="P8">
-        <v>0.5093213701657459</v>
+        <v>19.21302027199633</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R8">
-        <v>0.5093213701657459</v>
+        <v>19</v>
       </c>
       <c r="S8" t="s">
         <v>50</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.2015336802044807</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>-0.2130202719963314</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>0.4953563430886915</v>
+        <v>14.16303197882762</v>
       </c>
       <c r="X8">
-        <v>0.01396502707705438</v>
+        <v>4.848454612964233</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>0.01148659179185074</v>
       </c>
       <c r="Z8">
-        <v>1.055164654914086</v>
+        <v>0.909013052069676</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>0.00215356493895383</v>
       </c>
       <c r="AB8">
-        <v>0.317384338170467</v>
+        <v>1.088521810556096</v>
       </c>
       <c r="AC8">
-        <v>50.36583963684151</v>
+        <v>55.34343008256245</v>
       </c>
       <c r="AD8" t="s">
         <v>52</v>
@@ -1244,82 +1247,82 @@
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>10.056</v>
+        <v>1.084</v>
       </c>
       <c r="D9">
-        <v>11.612</v>
+        <v>1.172</v>
       </c>
       <c r="E9">
-        <v>12.72721886527684</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="F9">
-        <v>11.6</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>10.78735901531492</v>
+        <v>1.125362206521666</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>12.72721886527684</v>
+        <v>1.761149755943273</v>
       </c>
       <c r="L9">
-        <v>3.050242274051084</v>
+        <v>0.8500971208676269</v>
       </c>
       <c r="M9">
         <v>1.038416113387647</v>
       </c>
       <c r="N9">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="s">
         <v>48</v>
       </c>
       <c r="P9">
-        <v>14.76027887619046</v>
+        <v>2.00997599986936</v>
       </c>
       <c r="Q9">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R9">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="S9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T9">
-        <v>2.033060010913617</v>
+        <v>0.2488262439260871</v>
       </c>
       <c r="U9">
-        <v>0.2397211238095416</v>
+        <v>-0.009975999869360042</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>10.78735901531492</v>
+        <v>1.125362206521666</v>
       </c>
       <c r="X9">
-        <v>1.939859849961922</v>
+        <v>0.6357875494216065</v>
       </c>
       <c r="Y9">
-        <v>2.272781134723159</v>
+        <v>0.2388502440567271</v>
       </c>
       <c r="Z9">
-        <v>0.6359691052952189</v>
+        <v>0.7478998973349168</v>
       </c>
       <c r="AA9">
-        <v>0.7451149549850793</v>
+        <v>0.2809681837446426</v>
       </c>
       <c r="AB9">
-        <v>0.544686120366265</v>
+        <v>1.700194241735254</v>
       </c>
       <c r="AC9">
-        <v>50.95791180581695</v>
+        <v>55.73990894075605</v>
       </c>
       <c r="AD9" t="s">
         <v>52</v>
@@ -1333,79 +1336,79 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>1.092</v>
+        <v>0.552</v>
       </c>
       <c r="D10">
-        <v>1.224</v>
+        <v>0.392</v>
       </c>
       <c r="E10">
-        <v>0.5513716620292705</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="G10">
-        <v>1.155708792388448</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>0.5513716620292705</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="L10">
-        <v>0.8200692764238203</v>
+        <v>0.3921195507989373</v>
       </c>
       <c r="M10">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N10">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="s">
         <v>48</v>
       </c>
       <c r="P10">
-        <v>0.5680132525146347</v>
+        <v>0.3085361649247209</v>
       </c>
       <c r="Q10">
-        <v>1.030182165010288</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T10">
-        <v>0.01664159048536429</v>
+        <v>0.03819542872082443</v>
       </c>
       <c r="U10">
-        <v>0.4319867474853653</v>
+        <v>-0.3085361649247209</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>1.155708792388448</v>
+        <v>0.4767959881424244</v>
       </c>
       <c r="X10">
-        <v>0.6043371303591779</v>
+        <v>0.206455251938528</v>
       </c>
       <c r="Y10">
-        <v>0.4486283379707295</v>
+        <v>0.2703407362038964</v>
       </c>
       <c r="Z10">
-        <v>0.7369342416955152</v>
+        <v>0.526510987574781</v>
       </c>
       <c r="AA10">
-        <v>0.5470615115921911</v>
+        <v>0.6894344738819614</v>
       </c>
       <c r="AB10">
-        <v>0.7455175240216548</v>
+        <v>0.6535325846648956</v>
       </c>
       <c r="AC10">
-        <v>51.14636374435788</v>
+        <v>55.79230620253968</v>
       </c>
       <c r="AD10" t="s">
         <v>52</v>
@@ -1416,82 +1419,82 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11">
-        <v>1.58</v>
+        <v>0.716</v>
       </c>
       <c r="D11">
-        <v>1.896</v>
+        <v>0.66</v>
       </c>
       <c r="E11">
-        <v>-0.7504271689963384</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="F11">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="G11">
-        <v>1.728527923418711</v>
+        <v>0.6896785958498485</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>0.9608490161719081</v>
       </c>
       <c r="L11">
-        <v>1.736334852416627</v>
+        <v>0.3332002265469857</v>
       </c>
       <c r="M11">
         <v>1.038416113387647</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="O11" t="s">
         <v>48</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1.096603770057717</v>
       </c>
       <c r="Q11">
-        <v>0.8172324090351291</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.135754753885809</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>-0.09660377005771714</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>1.728527923418711</v>
+        <v>0.6896785958498485</v>
       </c>
       <c r="X11">
-        <v>1.728527923418711</v>
+        <v>0.2711704203220596</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>0.0391509838280919</v>
       </c>
       <c r="Z11">
-        <v>0.9955037883464413</v>
+        <v>0.813836242346675</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.1174998715751806</v>
       </c>
       <c r="AB11">
-        <v>0.5601080169085895</v>
+        <v>0.5553337109116429</v>
       </c>
       <c r="AC11">
-        <v>52.35737067882981</v>
+        <v>56.54584207939454</v>
       </c>
       <c r="AD11" t="s">
         <v>52</v>
@@ -1502,28 +1505,28 @@
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12">
-        <v>1.88</v>
+        <v>1.832</v>
       </c>
       <c r="D12">
-        <v>1.824</v>
+        <v>1.772</v>
       </c>
       <c r="E12">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="F12">
         <v>1.6</v>
       </c>
       <c r="G12">
-        <v>1.852972027471568</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="J12" t="s">
         <v>4</v>
       </c>
       <c r="K12">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="L12">
         <v>1.198624596172324</v>
@@ -1538,46 +1541,46 @@
         <v>48</v>
       </c>
       <c r="P12">
-        <v>2.83326060636738</v>
+        <v>2.528722469358031</v>
       </c>
       <c r="Q12">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T12">
-        <v>-0.1926464925408</v>
+        <v>-0.02592202596419435</v>
       </c>
       <c r="U12">
-        <v>0.1667393936326196</v>
+        <v>-0.5287224693580312</v>
       </c>
       <c r="V12" t="s">
         <v>6</v>
       </c>
       <c r="W12">
-        <v>1.852972027471568</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="X12">
-        <v>1.172935071436613</v>
+        <v>0.7516030373169746</v>
       </c>
       <c r="Y12">
-        <v>0.02590709890818044</v>
+        <v>0.5546444953222256</v>
       </c>
       <c r="Z12">
-        <v>0.9785674974318499</v>
+        <v>0.627054575483547</v>
       </c>
       <c r="AA12">
-        <v>0.02161402243113641</v>
+        <v>0.4627341179994319</v>
       </c>
       <c r="AB12">
         <v>0.7491403726077025</v>
       </c>
       <c r="AC12">
-        <v>52.53798358234432</v>
+        <v>56.57842736664286</v>
       </c>
       <c r="AD12" t="s">
         <v>52</v>
@@ -1588,82 +1591,82 @@
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13">
-        <v>0.544</v>
+        <v>8.612</v>
       </c>
       <c r="D13">
-        <v>0.372</v>
+        <v>6.564</v>
       </c>
       <c r="E13">
-        <v>0.2302122475795285</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="F13">
-        <v>0.4</v>
+        <v>6.6</v>
       </c>
       <c r="G13">
-        <v>0.4631556872531063</v>
+        <v>7.623548433245896</v>
       </c>
       <c r="J13" t="s">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>0.2302122475795285</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="L13">
-        <v>0.3921195507989373</v>
+        <v>4.673523904256721</v>
       </c>
       <c r="M13">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N13">
-        <v>0.6</v>
+        <v>8.4</v>
       </c>
       <c r="O13" t="s">
         <v>48</v>
       </c>
       <c r="P13">
-        <v>0.2669866064972812</v>
+        <v>3.770163053558897</v>
       </c>
       <c r="Q13">
-        <v>1.159741105455516</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T13">
-        <v>0.03677435891775274</v>
+        <v>-0.03864807852496854</v>
       </c>
       <c r="U13">
-        <v>-0.2669866064972812</v>
+        <v>0.229836946441103</v>
       </c>
       <c r="V13" t="s">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>0.4631556872531063</v>
+        <v>7.623548433245896</v>
       </c>
       <c r="X13">
-        <v>0.2329434396735778</v>
+        <v>3.81473730116203</v>
       </c>
       <c r="Y13">
-        <v>0.2302122475795285</v>
+        <v>0.1911888679161344</v>
       </c>
       <c r="Z13">
-        <v>0.5940622934994169</v>
+        <v>0.816244311425797</v>
       </c>
       <c r="AA13">
-        <v>0.5870970909521719</v>
+        <v>0.04090893121184135</v>
       </c>
       <c r="AB13">
-        <v>0.6535325846648956</v>
+        <v>0.5563718933638954</v>
       </c>
       <c r="AC13">
-        <v>55.34275262590184</v>
+        <v>57.99131498158366</v>
       </c>
       <c r="AD13" t="s">
         <v>52</v>
@@ -1674,85 +1677,85 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14">
-        <v>0.412</v>
+        <v>3.54</v>
       </c>
       <c r="D14">
-        <v>0.552</v>
+        <v>4.812</v>
       </c>
       <c r="E14">
-        <v>1.125104248703698</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="F14">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="G14">
-        <v>0.4778035103753786</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="J14" t="s">
         <v>4</v>
       </c>
       <c r="K14">
-        <v>1.125104248703698</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="L14">
-        <v>0.8079772006265793</v>
+        <v>2.262338789582505</v>
       </c>
       <c r="M14">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N14">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="O14" t="s">
         <v>48</v>
       </c>
       <c r="P14">
-        <v>0.9194716555837816</v>
+        <v>5.645415907992541</v>
       </c>
       <c r="Q14">
-        <v>0.8172324090351291</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="S14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T14">
-        <v>-0.2056325931199159</v>
+        <v>0.05921720937758934</v>
       </c>
       <c r="U14">
-        <v>0.08052834441621837</v>
+        <v>0.3545840920074594</v>
       </c>
       <c r="V14" t="s">
         <v>6</v>
       </c>
       <c r="W14">
-        <v>0.4778035103753786</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="X14">
-        <v>0.6473007383283189</v>
+        <v>1.432277608326268</v>
       </c>
       <c r="Y14">
-        <v>0.1251042487036975</v>
+        <v>0.4138013013850488</v>
       </c>
       <c r="Z14">
-        <v>0.80113738088939</v>
+        <v>0.633095986737947</v>
       </c>
       <c r="AA14">
-        <v>0.1548363599946635</v>
+        <v>0.1829086356519627</v>
       </c>
       <c r="AB14">
-        <v>1.346628667710966</v>
+        <v>0.452467757916501</v>
       </c>
       <c r="AC14">
-        <v>56.27431207716731</v>
+        <v>62.15552874778314</v>
       </c>
       <c r="AD14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:30">
@@ -1763,82 +1766,82 @@
         <v>46</v>
       </c>
       <c r="C15">
-        <v>13.792</v>
+        <v>0.676</v>
       </c>
       <c r="D15">
-        <v>14.964</v>
+        <v>0.612</v>
       </c>
       <c r="E15">
-        <v>18.4418098343119</v>
+        <v>-0.005331174175850051</v>
       </c>
       <c r="F15">
-        <v>14.6</v>
+        <v>0.6</v>
       </c>
       <c r="G15">
-        <v>14.35765685363077</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="J15" t="s">
         <v>4</v>
       </c>
       <c r="K15">
-        <v>18.4418098343119</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>5.333756871724871</v>
+        <v>1.005444112310955</v>
       </c>
       <c r="M15">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N15">
-        <v>4.9</v>
+        <v>0.9</v>
       </c>
       <c r="O15" t="s">
         <v>48</v>
       </c>
       <c r="P15">
-        <v>18.99842358181946</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>1.030182165010288</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T15">
-        <v>0.556613747507555</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>0.001576418180540884</v>
+        <v>0</v>
       </c>
       <c r="V15" t="s">
         <v>6</v>
       </c>
       <c r="W15">
-        <v>14.35765685363077</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="X15">
-        <v>4.084152980681136</v>
+        <v>0.6459183952569697</v>
       </c>
       <c r="Y15">
-        <v>0.5581901656880959</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>0.7657178755807014</v>
+        <v>0.642420983273117</v>
       </c>
       <c r="AA15">
-        <v>0.1046523452628961</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.088521810556096</v>
+        <v>1.117160124789949</v>
       </c>
       <c r="AC15">
-        <v>58.6053064371732</v>
+        <v>65.86429881671735</v>
       </c>
       <c r="AD15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:30">
@@ -1849,82 +1852,82 @@
         <v>46</v>
       </c>
       <c r="C16">
-        <v>13.488</v>
+        <v>0.368</v>
       </c>
       <c r="D16">
-        <v>12.544</v>
+        <v>0.512</v>
       </c>
       <c r="E16">
-        <v>15.02106749310035</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="F16">
-        <v>11.8</v>
+        <v>0.4</v>
       </c>
       <c r="G16">
-        <v>13.03238560594928</v>
+        <v>0.4356836106718179</v>
       </c>
       <c r="J16" t="s">
         <v>4</v>
       </c>
       <c r="K16">
-        <v>15.02106749310035</v>
+        <v>0.8003007397713651</v>
       </c>
       <c r="L16">
-        <v>3.125306797245826</v>
+        <v>0.8079772006265793</v>
       </c>
       <c r="M16">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N16">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="s">
         <v>48</v>
       </c>
       <c r="P16">
-        <v>14.06474072159816</v>
+        <v>0.689041649067501</v>
       </c>
       <c r="Q16">
-        <v>0.9363343003457338</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R16">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T16">
-        <v>-0.956326771502189</v>
+        <v>-0.1112590907038641</v>
       </c>
       <c r="U16">
-        <v>-0.06474072159816124</v>
+        <v>0.310958350932499</v>
       </c>
       <c r="V16" t="s">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>13.03238560594928</v>
+        <v>0.4356836106718179</v>
       </c>
       <c r="X16">
-        <v>1.988681887151071</v>
+        <v>0.3646171290995471</v>
       </c>
       <c r="Y16">
-        <v>1.02106749310035</v>
+        <v>0.1996992602286349</v>
       </c>
       <c r="Z16">
-        <v>0.6363157335156967</v>
+        <v>0.4512715566934187</v>
       </c>
       <c r="AA16">
-        <v>0.3267095230459183</v>
+        <v>0.247159523899647</v>
       </c>
       <c r="AB16">
-        <v>0.6511055827595471</v>
+        <v>1.346628667710966</v>
       </c>
       <c r="AC16">
-        <v>58.9810747875693</v>
+        <v>68.39760714610466</v>
       </c>
       <c r="AD16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
